--- a/tabtools/qa/output/regtab_ext_test1.xlsx
+++ b/tabtools/qa/output/regtab_ext_test1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="450" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="495" uniqueCount="23">
   <si>
     <t>Test 1: Logistic with Stats</t>
   </si>
@@ -88,10 +88,954 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="2201">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="2421">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -9542,7 +10486,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1681">
+  <borders count="1849">
     <border>
       <left/>
       <right/>
@@ -21010,11 +21954,1157 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1681">
+  <cellXfs count="1849">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -27583,6 +29673,663 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="2200" fillId="0" borderId="1680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1681" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1682" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1683" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1684" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1685" xfId="0"/>
+    <xf numFmtId="0" fontId="2201" fillId="0" borderId="1686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2202" fillId="0" borderId="1687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2203" fillId="0" borderId="1688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2204" fillId="0" borderId="1689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2205" fillId="0" borderId="1690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2206" fillId="0" borderId="1691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2208" fillId="0" borderId="1692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2210" fillId="0" borderId="1693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2212" fillId="0" borderId="1694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2213" fillId="0" borderId="1695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2214" fillId="0" borderId="1696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2215" fillId="0" borderId="1697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2216" fillId="0" borderId="1698" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2217" fillId="0" borderId="1699" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2218" fillId="0" borderId="1700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2219" fillId="0" borderId="1701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2220" fillId="0" borderId="1702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2221" fillId="0" borderId="1703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2222" fillId="0" borderId="1704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2223" fillId="0" borderId="1705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2224" fillId="0" borderId="1706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2225" fillId="0" borderId="1707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2226" fillId="0" borderId="1708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2227" fillId="0" borderId="1709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2228" fillId="0" borderId="1710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2229" fillId="0" borderId="1711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2230" fillId="0" borderId="1712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2231" fillId="0" borderId="1713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2232" fillId="0" borderId="1714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2233" fillId="0" borderId="1715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2235" fillId="0" borderId="1716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2237" fillId="0" borderId="1717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2239" fillId="0" borderId="1718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2241" fillId="0" borderId="1719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2243" fillId="0" borderId="1720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2244" fillId="0" borderId="1721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2245" fillId="0" borderId="1722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2246" fillId="0" borderId="1723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2247" fillId="0" borderId="1724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2248" fillId="0" borderId="1725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2249" fillId="0" borderId="1726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2250" fillId="0" borderId="1727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2251" fillId="0" borderId="1728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2252" fillId="0" borderId="1729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2253" fillId="0" borderId="1730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2254" fillId="0" borderId="1731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2255" fillId="0" borderId="1732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2256" fillId="0" borderId="1733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2258" fillId="0" borderId="1734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2260" fillId="0" borderId="1735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2262" fillId="0" borderId="1736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2264" fillId="0" borderId="1737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2265" fillId="0" borderId="1738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2266" fillId="0" borderId="1739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2267" fillId="0" borderId="1740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2268" fillId="0" borderId="1741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2269" fillId="0" borderId="1742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2270" fillId="0" borderId="1743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2271" fillId="0" borderId="1744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2272" fillId="0" borderId="1745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2273" fillId="0" borderId="1746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2274" fillId="0" borderId="1747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2275" fillId="0" borderId="1748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2276" fillId="0" borderId="1749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2277" fillId="0" borderId="1750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2278" fillId="0" borderId="1751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2279" fillId="0" borderId="1752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2280" fillId="0" borderId="1753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2281" fillId="0" borderId="1754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2282" fillId="0" borderId="1755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2283" fillId="0" borderId="1756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2284" fillId="0" borderId="1757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2285" fillId="0" borderId="1758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2286" fillId="0" borderId="1759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2287" fillId="0" borderId="1760" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2288" fillId="0" borderId="1761" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2289" fillId="0" borderId="1762" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2290" fillId="0" borderId="1763" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2291" fillId="0" borderId="1764" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2292" fillId="0" borderId="1765" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2293" fillId="0" borderId="1766" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2294" fillId="0" borderId="1767" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2295" fillId="0" borderId="1768" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2296" fillId="0" borderId="1769" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2297" fillId="0" borderId="1770" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2298" fillId="0" borderId="1771" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2299" fillId="0" borderId="1772" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2300" fillId="0" borderId="1773" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2301" fillId="0" borderId="1774" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2302" fillId="0" borderId="1775" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2303" fillId="0" borderId="1776" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2304" fillId="0" borderId="1777" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2305" fillId="0" borderId="1778" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2306" fillId="0" borderId="1779" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2307" fillId="0" borderId="1780" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2308" fillId="0" borderId="1781" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2309" fillId="0" borderId="1782" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2310" fillId="0" borderId="1783" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2311" fillId="0" borderId="1784" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2312" fillId="0" borderId="1785" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2313" fillId="0" borderId="1786" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2314" fillId="0" borderId="1787" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2315" fillId="0" borderId="1788" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2316" fillId="0" borderId="1789" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2317" fillId="0" borderId="1790" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2318" fillId="0" borderId="1791" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2319" fillId="0" borderId="1792" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2320" fillId="0" borderId="1793" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2321" fillId="0" borderId="1794" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2322" fillId="0" borderId="1795" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2323" fillId="0" borderId="1796" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2324" fillId="0" borderId="1797" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2325" fillId="0" borderId="1798" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2326" fillId="0" borderId="1799" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2327" fillId="0" borderId="1800" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2328" fillId="0" borderId="1801" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2329" fillId="0" borderId="1802" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2330" fillId="0" borderId="1803" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2332" fillId="0" borderId="1804" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2334" fillId="0" borderId="1805" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2336" fillId="0" borderId="1806" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2338" fillId="0" borderId="1807" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2340" fillId="0" borderId="1808" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2342" fillId="0" borderId="1809" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2344" fillId="0" borderId="1810" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2346" fillId="0" borderId="1811" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2348" fillId="0" borderId="1812" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2350" fillId="0" borderId="1813" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2352" fillId="0" borderId="1814" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2354" fillId="0" borderId="1815" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2356" fillId="0" borderId="1816" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2358" fillId="0" borderId="1817" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2360" fillId="0" borderId="1818" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2362" fillId="0" borderId="1819" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2364" fillId="0" borderId="1820" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2366" fillId="0" borderId="1821" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2368" fillId="0" borderId="1822" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2370" fillId="0" borderId="1823" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2372" fillId="0" borderId="1824" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2374" fillId="0" borderId="1825" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2376" fillId="0" borderId="1826" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2378" fillId="0" borderId="1827" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2380" fillId="0" borderId="1828" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2382" fillId="0" borderId="1829" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2384" fillId="0" borderId="1830" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2386" fillId="0" borderId="1831" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2388" fillId="0" borderId="1832" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2390" fillId="0" borderId="1833" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2392" fillId="0" borderId="1834" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2394" fillId="0" borderId="1835" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2396" fillId="0" borderId="1836" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2398" fillId="0" borderId="1837" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2400" fillId="0" borderId="1838" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2402" fillId="0" borderId="1839" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2404" fillId="0" borderId="1840" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2406" fillId="0" borderId="1841" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2408" fillId="0" borderId="1842" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2410" fillId="0" borderId="1843" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2412" fillId="0" borderId="1844" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2414" fillId="0" borderId="1845" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2416" fillId="0" borderId="1846" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2418" fillId="0" borderId="1847" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2420" fillId="0" borderId="1848" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -27598,162 +30345,162 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.7109375" style="1514" customWidth="true"/>
-    <col min="3" max="3" width="5.11328125" style="1515" customWidth="true"/>
-    <col min="4" max="4" width="11.11328125" style="1516" customWidth="true"/>
-    <col min="5" max="5" width="7.7109375" style="1517" customWidth="true"/>
+    <col min="2" max="2" width="13.7109375" style="1682" customWidth="true"/>
+    <col min="3" max="3" width="5.11328125" style="1683" customWidth="true"/>
+    <col min="4" max="4" width="11.11328125" style="1684" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="1685" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="1513" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="1636" t="s">
+    <row r="1" s="1681" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="1804" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1637" t="s">
+      <c r="B1" s="1805" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1638" t="s">
+      <c r="C1" s="1806" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1639" t="s">
+      <c r="D1" s="1807" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1640" t="s">
+      <c r="E1" s="1808" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1641" t="s">
+      <c r="A2" s="1809" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1642" t="s">
+      <c r="B2" s="1810" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1643" t="s">
+      <c r="C2" s="1811" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1644" t="s">
+      <c r="D2" s="1812" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1645" t="s">
+      <c r="E2" s="1813" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1646" t="s">
+      <c r="A3" s="1814" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1647" t="s">
+      <c r="B3" s="1815" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1648" t="s">
+      <c r="C3" s="1816" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1649" t="s">
+      <c r="D3" s="1817" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="1650" t="s">
+      <c r="E3" s="1818" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1651" t="s">
+      <c r="A4" s="1819" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="1652" t="s">
+      <c r="B4" s="1820" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="1653" t="s">
+      <c r="C4" s="1821" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="1654" t="s">
+      <c r="D4" s="1822" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="1655" t="s">
+      <c r="E4" s="1823" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1656" t="s">
+      <c r="A5" s="1824" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="1657" t="s">
+      <c r="B5" s="1825" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="1658" t="s">
+      <c r="C5" s="1826" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="1659" t="s">
+      <c r="D5" s="1827" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="1660" t="s">
+      <c r="E5" s="1828" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1661" t="s">
+      <c r="A6" s="1829" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="1662" t="s">
+      <c r="B6" s="1830" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="1663" t="s">
+      <c r="C6" s="1831" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="1664" t="s">
+      <c r="D6" s="1832" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="1665" t="s">
+      <c r="E6" s="1833" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1666" t="s">
+      <c r="A7" s="1834" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="1667" t="s">
+      <c r="B7" s="1835" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="1668" t="s">
+      <c r="C7" s="1836" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="1669" t="s">
+      <c r="D7" s="1837" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="1670" t="s">
+      <c r="E7" s="1838" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1671" t="s">
+      <c r="A8" s="1839" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="1672" t="s">
+      <c r="B8" s="1840" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="1673" t="s">
+      <c r="C8" s="1841" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="1674" t="s">
+      <c r="D8" s="1842" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="1675" t="s">
+      <c r="E8" s="1843" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1676" t="s">
+      <c r="A9" s="1844" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="1677" t="s">
+      <c r="B9" s="1845" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="1678" t="s">
+      <c r="C9" s="1846" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="1679" t="s">
+      <c r="D9" s="1847" t="s">
         <v>1</v>
       </c>
-      <c r="E9" s="1680" t="s">
+      <c r="E9" s="1848" t="s">
         <v>1</v>
       </c>
     </row>
